--- a/modelos/OdP's de cada funcionário.xlsx
+++ b/modelos/OdP's de cada funcionário.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/484c53c37b433491/Desktop/Projetos/Transformers - Convertedor de arquivos/modelos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_69D1BB207A00D00DEC82CC547798B416B8469308" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EECA012-FB6A-4718-9F39-15D5CDC62579}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_69D1BB207A00D00DEC82CC547798B416B8469308" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1011B5D-9C9D-464D-9055-94FADC940A79}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,22 +83,26 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="30"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -106,11 +110,13 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -128,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -238,31 +244,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -290,14 +276,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -307,6 +285,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,28 +510,29 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" customWidth="1"/>
-    <col min="7" max="7" width="29.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" customWidth="1"/>
-    <col min="11" max="11" width="75.7109375" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" customWidth="1"/>
+    <col min="11" max="11" width="21.5703125" customWidth="1"/>
+    <col min="12" max="12" width="75.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11"/>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
@@ -559,10 +541,11 @@
       <c r="I1" s="10"/>
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
     </row>
-    <row r="2" spans="1:26" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12"/>
-      <c r="B2" s="10"/>
+    <row r="2" spans="1:27" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -572,74 +555,77 @@
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
     </row>
-    <row r="3" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="9"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="8"/>
+      <c r="J3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="17"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="13"/>
     </row>
-    <row r="4" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14"/>
+    <row r="4" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="18"/>
       <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
       <c r="F4" s="16"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="20"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
       <c r="K4" s="16"/>
+      <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:26" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="1:27" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -649,24 +635,25 @@
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
-      <c r="V5" s="4"/>
+      <c r="V5" s="3"/>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K6" s="5"/>
+    <row r="6" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L6" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B1:K2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="C1:L2"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A3:B5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/modelos/OdP's de cada funcionário.xlsx
+++ b/modelos/OdP's de cada funcionário.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/484c53c37b433491/Desktop/Projetos/Transformers - Convertedor de arquivos/modelos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_69D1BB207A00D00DEC82CC547798B416B8469308" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1011B5D-9C9D-464D-9055-94FADC940A79}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_69D1BB207A00D00DEC82CC547798B416B8469308" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{292F49C2-A142-444C-8822-BBC77686D79C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Página1" sheetId="1" r:id="rId1"/>
+    <sheet name="Modelo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>OPERADOR:</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>OBS</t>
+  </si>
+  <si>
+    <t>OP MATERIAL</t>
+  </si>
+  <si>
+    <t>OP TUBETE</t>
   </si>
   <si>
     <t>ODP´S DE CADA FUNCIONÁRIO</t>
@@ -83,26 +89,22 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="30"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -110,13 +112,11 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -134,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -146,6 +146,28 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -156,6 +178,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -227,6 +269,24 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -244,16 +304,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -263,30 +354,62 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,93 +633,104 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="2" max="3" width="22.85546875" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" customWidth="1"/>
     <col min="5" max="5" width="17.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-    <col min="8" max="8" width="29.140625" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="75.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.85546875" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" customWidth="1"/>
+    <col min="11" max="11" width="48.5703125" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="75.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18"/>
-      <c r="B1" s="18"/>
-      <c r="C1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:27" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
+    <row r="2" spans="1:29" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
+    <row r="3" spans="1:29" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="8" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="7"/>
+      <c r="L3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="13"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="9"/>
     </row>
-    <row r="4" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="16"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="12"/>
       <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="10"/>
     </row>
-    <row r="5" spans="1:27" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="6" t="s">
+    <row r="5" spans="1:29" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -606,28 +740,32 @@
         <v>6</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
@@ -636,24 +774,26 @@
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
     </row>
-    <row r="6" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L6" s="5"/>
+    <row r="6" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="N6" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C1:L2"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="N3:N4"/>
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="J4:M4"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A3:B5"/>
+    <mergeCell ref="C1:N2"/>
+    <mergeCell ref="G3:I4"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/modelos/OdP's de cada funcionário.xlsx
+++ b/modelos/OdP's de cada funcionário.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/484c53c37b433491/Desktop/Projetos/Transformers - Convertedor de arquivos/modelos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_69D1BB207A00D00DEC82CC547798B416B8469308" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{292F49C2-A142-444C-8822-BBC77686D79C}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="11_69D1BB207A00D00DEC82CC547798B416B8469308" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28BBAA9D-0255-4CF3-BD4C-B43EA4BB44FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modelo" sheetId="1" r:id="rId1"/>
+    <sheet name="historico_modelo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>OPERADOR:</t>
   </si>
@@ -71,13 +72,37 @@
   </si>
   <si>
     <t>ODP´S DE CADA FUNCIONÁRIO</t>
+  </si>
+  <si>
+    <t>HISTÓRICO</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>HORA</t>
+  </si>
+  <si>
+    <t>IDENTIFICADOR</t>
+  </si>
+  <si>
+    <t>ODP</t>
+  </si>
+  <si>
+    <t>AÇÃO</t>
+  </si>
+  <si>
+    <t>VALOR ANTERIOR</t>
+  </si>
+  <si>
+    <t>NOVO VALOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -119,6 +144,20 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -134,7 +173,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -221,17 +260,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -306,47 +334,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -354,18 +358,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -378,28 +376,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -410,6 +399,60 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -649,151 +692,258 @@
     <col min="12" max="12" width="19.85546875" customWidth="1"/>
     <col min="13" max="13" width="21.5703125" customWidth="1"/>
     <col min="14" max="14" width="75.7109375" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" customWidth="1"/>
+    <col min="18" max="18" width="19.42578125" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14"/>
-      <c r="B1" s="14"/>
-      <c r="C1" s="22" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="6"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
     </row>
     <row r="2" spans="1:29" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="6"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
     </row>
-    <row r="3" spans="1:29" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="7" t="s">
+    <row r="3" spans="1:29" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
+      <c r="D3" s="23"/>
+      <c r="E3" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="7" t="s">
+      <c r="F3" s="24"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="23"/>
+      <c r="L3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="9"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="10"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
     </row>
     <row r="5" spans="1:29" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
+      <c r="O5" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
     </row>
     <row r="6" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="N6" s="5"/>
+      <c r="N6" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="N3:N4"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A3:B5"/>
-    <mergeCell ref="C1:N2"/>
     <mergeCell ref="G3:I4"/>
+    <mergeCell ref="C1:S2"/>
+    <mergeCell ref="N3:S4"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88BC175-D680-46AF-B115-61DFC37BBD7C}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="1.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="3" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:I2"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
